--- a/template fix final transaksi.xlsx
+++ b/template fix final transaksi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/erwinpranata/Documents/www/bjb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59093C17-C21C-5643-A81F-143B1DC6EB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBC020AF-DF32-1344-BB7B-1799E7DC6347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{A7149291-5796-C348-B4DC-A2F9F969C97D}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>BULAN</t>
   </si>
@@ -78,12 +78,6 @@
   <si>
     <t>PPh Final
 Harus Dibayar</t>
-  </si>
-  <si>
-    <t>STATIC</t>
-  </si>
-  <si>
-    <t>DYNAMIC</t>
   </si>
   <si>
     <t>Cabang 2</t>
@@ -96,7 +90,7 @@
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -131,9 +125,35 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -158,37 +178,51 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -509,624 +543,675 @@
   <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="14" width="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="14" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="18.5" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="C1" s="11" t="s">
+    <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="8"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-    </row>
-    <row r="2" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C2" s="2">
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+    </row>
+    <row r="2" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="16">
         <v>1</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="16">
         <v>2</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="16">
         <v>3</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="16">
         <v>4</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="16">
         <v>5</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="16">
         <v>6</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="16">
         <v>7</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="16">
         <v>8</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="16">
         <v>9</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="16">
         <v>10</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="16">
         <v>11</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" s="16">
         <v>12</v>
       </c>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" s="12" t="s">
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+    </row>
+    <row r="3" spans="1:16" ht="21" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="10">
         <v>300000000</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="10">
         <v>300000000</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="10">
         <v>300000000</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="10">
         <v>300000000</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="10">
         <v>300000000</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3" s="10">
         <v>300000000</v>
       </c>
-      <c r="I3" s="1">
+      <c r="I3" s="10">
         <v>300000000</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="10">
         <v>300000000</v>
       </c>
-      <c r="K3" s="1">
+      <c r="K3" s="10">
         <v>600000000</v>
       </c>
-      <c r="L3" s="1">
+      <c r="L3" s="10">
         <v>600000000</v>
       </c>
-      <c r="M3" s="1">
+      <c r="M3" s="10">
         <v>600000000</v>
       </c>
-      <c r="N3" s="1">
+      <c r="N3" s="10">
         <v>600000000</v>
       </c>
-      <c r="O3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="P3" s="10"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A4" s="12"/>
-      <c r="B4" t="s">
+      <c r="O3" s="5"/>
+      <c r="P3" s="4"/>
+    </row>
+    <row r="4" spans="1:16" ht="21" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+      <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="10"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A5" s="12"/>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="10"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
+      <c r="C4" s="10">
+        <v>100000000</v>
+      </c>
+      <c r="D4" s="10">
+        <v>100000000</v>
+      </c>
+      <c r="E4" s="10">
+        <v>100000000</v>
+      </c>
+      <c r="F4" s="10">
+        <v>100000000</v>
+      </c>
+      <c r="G4" s="10">
+        <v>100000000</v>
+      </c>
+      <c r="H4" s="10">
+        <v>100000000</v>
+      </c>
+      <c r="I4" s="10">
+        <v>100000000</v>
+      </c>
+      <c r="J4" s="10">
+        <v>100000000</v>
+      </c>
+      <c r="K4" s="10">
+        <v>100000000</v>
+      </c>
+      <c r="L4" s="10">
+        <v>200000000</v>
+      </c>
+      <c r="M4" s="10">
+        <v>200000000</v>
+      </c>
+      <c r="N4" s="10">
+        <v>200000000</v>
+      </c>
+      <c r="O4" s="5"/>
+      <c r="P4" s="4"/>
+    </row>
+    <row r="5" spans="1:16" ht="21" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="10">
+        <v>50000000</v>
+      </c>
+      <c r="D5" s="10">
+        <v>50000000</v>
+      </c>
+      <c r="E5" s="10">
+        <v>50000000</v>
+      </c>
+      <c r="F5" s="10">
+        <v>50000000</v>
+      </c>
+      <c r="G5" s="10">
+        <v>50000000</v>
+      </c>
+      <c r="H5" s="10">
+        <v>50000000</v>
+      </c>
+      <c r="I5" s="10">
+        <v>50000000</v>
+      </c>
+      <c r="J5" s="10">
+        <v>50000000</v>
+      </c>
+      <c r="K5" s="10">
+        <v>50000000</v>
+      </c>
+      <c r="L5" s="10">
+        <v>100000000</v>
+      </c>
+      <c r="M5" s="10">
+        <v>100000000</v>
+      </c>
+      <c r="N5" s="10">
+        <v>100000000</v>
+      </c>
+      <c r="O5" s="5"/>
+      <c r="P5" s="4"/>
+    </row>
+    <row r="6" spans="1:16" ht="21" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="J6" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="K6" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="L6" s="1">
+      <c r="C6" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="D6" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="E6" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="F6" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="G6" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="H6" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="I6" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="J6" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="K6" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="L6" s="10">
         <v>1500000</v>
       </c>
-      <c r="M6" s="1">
+      <c r="M6" s="10">
         <v>1500000</v>
       </c>
-      <c r="N6" s="1">
+      <c r="N6" s="10">
         <v>1500000</v>
       </c>
-      <c r="O6" s="8"/>
-      <c r="P6" s="10"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A7" s="12"/>
-      <c r="B7" t="s">
+      <c r="O6" s="5"/>
+      <c r="P6" s="4"/>
+    </row>
+    <row r="7" spans="1:16" ht="21" x14ac:dyDescent="0.25">
+      <c r="A7" s="7"/>
+      <c r="B7" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="D7" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="H7" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="J7" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="K7" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="L7" s="1">
+      <c r="C7" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="D7" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="E7" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="F7" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="G7" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="H7" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="I7" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="J7" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="K7" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="L7" s="10">
         <v>1500000</v>
       </c>
-      <c r="M7" s="1">
+      <c r="M7" s="10">
         <v>1500000</v>
       </c>
-      <c r="N7" s="1">
+      <c r="N7" s="10">
         <v>1500000</v>
       </c>
-      <c r="O7" s="8"/>
-      <c r="P7" s="10"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
-      <c r="B8" t="s">
+      <c r="O7" s="5"/>
+      <c r="P7" s="4"/>
+    </row>
+    <row r="8" spans="1:16" ht="21" x14ac:dyDescent="0.25">
+      <c r="A8" s="7"/>
+      <c r="B8" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="D8" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="H8" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="J8" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="K8" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="L8" s="1">
+      <c r="C8" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="D8" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="E8" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="F8" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="G8" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="H8" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="I8" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="J8" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="K8" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="L8" s="10">
         <v>1500000</v>
       </c>
-      <c r="M8" s="1">
+      <c r="M8" s="10">
         <v>1500000</v>
       </c>
-      <c r="N8" s="1">
+      <c r="N8" s="10">
         <v>1500000</v>
       </c>
-      <c r="O8" s="8"/>
-      <c r="P8" s="10"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
-      <c r="B9" t="s">
+      <c r="O8" s="5"/>
+      <c r="P8" s="4"/>
+    </row>
+    <row r="9" spans="1:16" ht="21" x14ac:dyDescent="0.25">
+      <c r="A9" s="7"/>
+      <c r="B9" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="D9" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="H9" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="I9" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="J9" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="K9" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="L9" s="1">
+      <c r="C9" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="D9" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="E9" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="F9" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="G9" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="H9" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="I9" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="J9" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="K9" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="L9" s="10">
         <v>1500000</v>
       </c>
-      <c r="M9" s="1">
+      <c r="M9" s="10">
         <v>1500000</v>
       </c>
-      <c r="N9" s="1">
+      <c r="N9" s="10">
         <v>1500000</v>
       </c>
-      <c r="O9" s="8"/>
-      <c r="P9" s="10"/>
-    </row>
-    <row r="10" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+      <c r="O9" s="5"/>
+      <c r="P9" s="4"/>
+    </row>
+    <row r="10" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
+      <c r="B10" s="11"/>
+      <c r="C10" s="12">
         <f t="shared" ref="C10:N10" si="0">SUM(C3:C9)</f>
-        <v>304000000</v>
-      </c>
-      <c r="D10" s="6">
+        <v>454000000</v>
+      </c>
+      <c r="D10" s="12">
         <f t="shared" si="0"/>
-        <v>304000000</v>
-      </c>
-      <c r="E10" s="6">
+        <v>454000000</v>
+      </c>
+      <c r="E10" s="12">
         <f t="shared" si="0"/>
-        <v>304000000</v>
-      </c>
-      <c r="F10" s="6">
+        <v>454000000</v>
+      </c>
+      <c r="F10" s="12">
         <f t="shared" si="0"/>
-        <v>304000000</v>
-      </c>
-      <c r="G10" s="6">
+        <v>454000000</v>
+      </c>
+      <c r="G10" s="12">
         <f t="shared" si="0"/>
-        <v>304000000</v>
-      </c>
-      <c r="H10" s="6">
+        <v>454000000</v>
+      </c>
+      <c r="H10" s="12">
         <f t="shared" si="0"/>
-        <v>304000000</v>
-      </c>
-      <c r="I10" s="6">
+        <v>454000000</v>
+      </c>
+      <c r="I10" s="12">
         <f t="shared" si="0"/>
-        <v>304000000</v>
-      </c>
-      <c r="J10" s="6">
+        <v>454000000</v>
+      </c>
+      <c r="J10" s="12">
         <f t="shared" si="0"/>
-        <v>304000000</v>
-      </c>
-      <c r="K10" s="6">
+        <v>454000000</v>
+      </c>
+      <c r="K10" s="12">
         <f t="shared" si="0"/>
-        <v>604000000</v>
-      </c>
-      <c r="L10" s="6">
+        <v>754000000</v>
+      </c>
+      <c r="L10" s="12">
         <f t="shared" si="0"/>
-        <v>606000000</v>
-      </c>
-      <c r="M10" s="6">
+        <v>906000000</v>
+      </c>
+      <c r="M10" s="12">
         <f t="shared" si="0"/>
-        <v>606000000</v>
-      </c>
-      <c r="N10" s="6">
+        <v>906000000</v>
+      </c>
+      <c r="N10" s="12">
         <f t="shared" si="0"/>
-        <v>606000000</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
+        <v>906000000</v>
+      </c>
+      <c r="O10" s="6"/>
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="1:16" ht="21" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="6">
+      <c r="B11" s="11"/>
+      <c r="C11" s="12">
         <f>C10*0.5%</f>
-        <v>1520000</v>
-      </c>
-      <c r="D11" s="6">
+        <v>2270000</v>
+      </c>
+      <c r="D11" s="12">
         <f t="shared" ref="D11:N11" si="1">D10*0.5%</f>
-        <v>1520000</v>
-      </c>
-      <c r="E11" s="6">
+        <v>2270000</v>
+      </c>
+      <c r="E11" s="12">
         <f t="shared" si="1"/>
-        <v>1520000</v>
-      </c>
-      <c r="F11" s="6">
+        <v>2270000</v>
+      </c>
+      <c r="F11" s="12">
         <f t="shared" si="1"/>
-        <v>1520000</v>
-      </c>
-      <c r="G11" s="6">
+        <v>2270000</v>
+      </c>
+      <c r="G11" s="12">
         <f t="shared" si="1"/>
-        <v>1520000</v>
-      </c>
-      <c r="H11" s="6">
+        <v>2270000</v>
+      </c>
+      <c r="H11" s="12">
         <f t="shared" si="1"/>
-        <v>1520000</v>
-      </c>
-      <c r="I11" s="6">
+        <v>2270000</v>
+      </c>
+      <c r="I11" s="12">
         <f t="shared" si="1"/>
-        <v>1520000</v>
-      </c>
-      <c r="J11" s="6">
+        <v>2270000</v>
+      </c>
+      <c r="J11" s="12">
         <f t="shared" si="1"/>
-        <v>1520000</v>
-      </c>
-      <c r="K11" s="6">
+        <v>2270000</v>
+      </c>
+      <c r="K11" s="12">
         <f t="shared" si="1"/>
-        <v>3020000</v>
-      </c>
-      <c r="L11" s="6">
+        <v>3770000</v>
+      </c>
+      <c r="L11" s="12">
         <f t="shared" si="1"/>
-        <v>3030000</v>
-      </c>
-      <c r="M11" s="6">
+        <v>4530000</v>
+      </c>
+      <c r="M11" s="12">
         <f t="shared" si="1"/>
-        <v>3030000</v>
-      </c>
-      <c r="N11" s="6">
+        <v>4530000</v>
+      </c>
+      <c r="N11" s="12">
         <f t="shared" si="1"/>
-        <v>3030000</v>
-      </c>
-      <c r="O11" s="9"/>
-    </row>
-    <row r="12" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
+        <v>4530000</v>
+      </c>
+      <c r="O11" s="6"/>
+    </row>
+    <row r="12" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="6">
+      <c r="B12" s="11"/>
+      <c r="C12" s="12">
         <f>C10</f>
-        <v>304000000</v>
-      </c>
-      <c r="D12" s="6">
+        <v>454000000</v>
+      </c>
+      <c r="D12" s="12">
         <f>C12+D10</f>
-        <v>608000000</v>
-      </c>
-      <c r="E12" s="6">
+        <v>908000000</v>
+      </c>
+      <c r="E12" s="12">
         <f t="shared" ref="E12:N12" si="2">D12+E10</f>
-        <v>912000000</v>
-      </c>
-      <c r="F12" s="6">
+        <v>1362000000</v>
+      </c>
+      <c r="F12" s="12">
         <f t="shared" si="2"/>
-        <v>1216000000</v>
-      </c>
-      <c r="G12" s="6">
+        <v>1816000000</v>
+      </c>
+      <c r="G12" s="12">
         <f t="shared" si="2"/>
-        <v>1520000000</v>
-      </c>
-      <c r="H12" s="6">
+        <v>2270000000</v>
+      </c>
+      <c r="H12" s="12">
         <f t="shared" si="2"/>
-        <v>1824000000</v>
-      </c>
-      <c r="I12" s="6">
+        <v>2724000000</v>
+      </c>
+      <c r="I12" s="12">
         <f t="shared" si="2"/>
-        <v>2128000000</v>
-      </c>
-      <c r="J12" s="6">
+        <v>3178000000</v>
+      </c>
+      <c r="J12" s="12">
         <f t="shared" si="2"/>
-        <v>2432000000</v>
-      </c>
-      <c r="K12" s="6">
+        <v>3632000000</v>
+      </c>
+      <c r="K12" s="12">
         <f t="shared" si="2"/>
-        <v>3036000000</v>
-      </c>
-      <c r="L12" s="6">
+        <v>4386000000</v>
+      </c>
+      <c r="L12" s="12">
         <f t="shared" si="2"/>
-        <v>3642000000</v>
-      </c>
-      <c r="M12" s="6">
+        <v>5292000000</v>
+      </c>
+      <c r="M12" s="12">
         <f t="shared" si="2"/>
-        <v>4248000000</v>
-      </c>
-      <c r="N12" s="6">
+        <v>6198000000</v>
+      </c>
+      <c r="N12" s="12">
         <f t="shared" si="2"/>
-        <v>4854000000</v>
-      </c>
-      <c r="O12" s="9"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
+        <v>7104000000</v>
+      </c>
+      <c r="O12" s="6"/>
+    </row>
+    <row r="13" spans="1:16" ht="21" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="6">
+      <c r="B13" s="11"/>
+      <c r="C13" s="12">
         <f>C12-500000000</f>
-        <v>-196000000</v>
-      </c>
-      <c r="D13" s="6">
-        <f t="shared" ref="D13:N13" si="3">D12-500000000</f>
-        <v>108000000</v>
-      </c>
-      <c r="E13" s="6">
+        <v>-46000000</v>
+      </c>
+      <c r="D13" s="12">
+        <f>D12-500000000</f>
+        <v>408000000</v>
+      </c>
+      <c r="E13" s="12">
+        <f t="shared" ref="D13:N13" si="3">E12-500000000</f>
+        <v>862000000</v>
+      </c>
+      <c r="F13" s="12">
         <f t="shared" si="3"/>
-        <v>412000000</v>
-      </c>
-      <c r="F13" s="6">
+        <v>1316000000</v>
+      </c>
+      <c r="G13" s="12">
         <f t="shared" si="3"/>
-        <v>716000000</v>
-      </c>
-      <c r="G13" s="6">
+        <v>1770000000</v>
+      </c>
+      <c r="H13" s="12">
         <f t="shared" si="3"/>
-        <v>1020000000</v>
-      </c>
-      <c r="H13" s="6">
+        <v>2224000000</v>
+      </c>
+      <c r="I13" s="12">
         <f t="shared" si="3"/>
-        <v>1324000000</v>
-      </c>
-      <c r="I13" s="6">
+        <v>2678000000</v>
+      </c>
+      <c r="J13" s="12">
         <f t="shared" si="3"/>
-        <v>1628000000</v>
-      </c>
-      <c r="J13" s="6">
+        <v>3132000000</v>
+      </c>
+      <c r="K13" s="12">
         <f t="shared" si="3"/>
-        <v>1932000000</v>
-      </c>
-      <c r="K13" s="6">
+        <v>3886000000</v>
+      </c>
+      <c r="L13" s="12">
         <f t="shared" si="3"/>
-        <v>2536000000</v>
-      </c>
-      <c r="L13" s="6">
+        <v>4792000000</v>
+      </c>
+      <c r="M13" s="12">
         <f t="shared" si="3"/>
-        <v>3142000000</v>
-      </c>
-      <c r="M13" s="6">
+        <v>5698000000</v>
+      </c>
+      <c r="N13" s="12">
         <f t="shared" si="3"/>
-        <v>3748000000</v>
-      </c>
-      <c r="N13" s="6">
-        <f t="shared" si="3"/>
-        <v>4354000000</v>
-      </c>
-      <c r="O13" s="9"/>
-    </row>
-    <row r="14" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
+        <v>6604000000</v>
+      </c>
+      <c r="O13" s="6"/>
+    </row>
+    <row r="14" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="3" t="str">
+      <c r="B14" s="11"/>
+      <c r="C14" s="14" t="str">
         <f>IF(C12&lt;500000000,"FREE",IF(#REF!="FREE",C13/200,C11))</f>
         <v>FREE</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="14">
         <f>IF(D12&lt;500000000,"FREE",IF(C14="FREE",D13/200,D11))</f>
-        <v>540000</v>
-      </c>
-      <c r="E14" s="3">
+        <v>2040000</v>
+      </c>
+      <c r="E14" s="14">
         <f t="shared" ref="E14:N14" si="4">IF(E12&lt;500000000,"FREE",IF(D14="FREE",E13/200,E11))</f>
-        <v>1520000</v>
-      </c>
-      <c r="F14" s="3">
+        <v>2270000</v>
+      </c>
+      <c r="F14" s="14">
         <f t="shared" si="4"/>
-        <v>1520000</v>
-      </c>
-      <c r="G14" s="3">
+        <v>2270000</v>
+      </c>
+      <c r="G14" s="14">
         <f t="shared" si="4"/>
-        <v>1520000</v>
-      </c>
-      <c r="H14" s="3">
+        <v>2270000</v>
+      </c>
+      <c r="H14" s="14">
         <f t="shared" si="4"/>
-        <v>1520000</v>
-      </c>
-      <c r="I14" s="3">
+        <v>2270000</v>
+      </c>
+      <c r="I14" s="14">
         <f t="shared" si="4"/>
-        <v>1520000</v>
-      </c>
-      <c r="J14" s="3">
+        <v>2270000</v>
+      </c>
+      <c r="J14" s="14">
         <f t="shared" si="4"/>
-        <v>1520000</v>
-      </c>
-      <c r="K14" s="3">
+        <v>2270000</v>
+      </c>
+      <c r="K14" s="14">
         <f t="shared" si="4"/>
-        <v>3020000</v>
-      </c>
-      <c r="L14" s="3">
+        <v>3770000</v>
+      </c>
+      <c r="L14" s="14">
         <f t="shared" si="4"/>
-        <v>3030000</v>
-      </c>
-      <c r="M14" s="3">
+        <v>4530000</v>
+      </c>
+      <c r="M14" s="14">
         <f t="shared" si="4"/>
-        <v>3030000</v>
-      </c>
-      <c r="N14" s="3">
+        <v>4530000</v>
+      </c>
+      <c r="N14" s="14">
         <f t="shared" si="4"/>
-        <v>3030000</v>
-      </c>
-      <c r="O14" s="9"/>
+        <v>4530000</v>
+      </c>
+      <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A15" s="4"/>
+      <c r="A15" s="2"/>
     </row>
     <row r="16" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="7">
     <mergeCell ref="C1:N1"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="O1:O2"/>
     <mergeCell ref="P1:P2"/>
-    <mergeCell ref="O3:O9"/>
-    <mergeCell ref="O10:O14"/>
     <mergeCell ref="P3:P5"/>
     <mergeCell ref="P6:P9"/>
   </mergeCells>
